--- a/data-manipulation-scripts/sheets-cleanup/sheets/PEDAL FREIO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PEDAL FREIO - 01_02.xlsx
@@ -438,7 +438,9 @@
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -450,7 +452,9 @@
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -460,7 +464,9 @@
       <c r="C5" s="2">
         <v>3.0</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="2">
+        <v>55.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -514,7 +520,9 @@
       <c r="C9" s="2">
         <v>2.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>47.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -554,7 +562,9 @@
       <c r="C12" s="2">
         <v>6.0</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -566,7 +576,9 @@
       <c r="C13" s="2">
         <v>2.0</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -592,7 +604,9 @@
       <c r="C15" s="2">
         <v>2.0</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="2">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -604,7 +618,9 @@
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3"/>
